--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{677DC8E8-422F-4DEE-A6B2-81373C481FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echan\IdeaProjects\selenium_prac\src\test\resources\testdata\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B01678-61FD-4096-9D12-6A72D6EF44B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Geolocation_Tracking_Data" sheetId="6" r:id="rId1"/>
@@ -40,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="142">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -105,17 +110,6 @@
     <t>Year</t>
   </si>
   <si>
-    <t>RS-TC-005
-RS-TC-007
-RS-TC-011
-RS-TC-015
-RS-TC-019
-RS-TC-020
-RS-TC-022
-RS-TC-026
-RS-TC-030</t>
-  </si>
-  <si>
     <t>Jane</t>
   </si>
   <si>
@@ -137,36 +131,24 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>RS-TC-004</t>
-  </si>
-  <si>
     <t>Jane123!</t>
   </si>
   <si>
     <t>Invalid First Name</t>
   </si>
   <si>
-    <t>RS-TC-006</t>
-  </si>
-  <si>
     <t>Doe123!</t>
   </si>
   <si>
     <t>Invalid Last Name</t>
   </si>
   <si>
-    <t>RS-TC-010</t>
-  </si>
-  <si>
     <t>janedoe.com</t>
   </si>
   <si>
     <t>Invalid Email</t>
   </si>
   <si>
-    <t>RS-TC-012</t>
-  </si>
-  <si>
     <t>testing!</t>
   </si>
   <si>
@@ -179,9 +161,6 @@
     <t>Invalid Phone Number Format</t>
   </si>
   <si>
-    <t>RS-TC-014</t>
-  </si>
-  <si>
     <t>RS-TC-016</t>
   </si>
   <si>
@@ -210,9 +189,6 @@
   </si>
   <si>
     <t>Invalid Confirm Password</t>
-  </si>
-  <si>
-    <t>RS-TC-031</t>
   </si>
   <si>
     <t>John</t>
@@ -463,12 +439,63 @@
   <si>
     <t>OS-TC-020</t>
   </si>
+  <si>
+    <t>RS-TC-005</t>
+  </si>
+  <si>
+    <t>RS-TC-008</t>
+  </si>
+  <si>
+    <t>091234567</t>
+  </si>
+  <si>
+    <t>RS-TC-022</t>
+  </si>
+  <si>
+    <t>RS-TC-023</t>
+  </si>
+  <si>
+    <t>RS-TC-026</t>
+  </si>
+  <si>
+    <t>RS-TC-030</t>
+  </si>
+  <si>
+    <t>Invalid Birthday (Future date)</t>
+  </si>
+  <si>
+    <t>RS-TC-011
+RS-TC-035</t>
+  </si>
+  <si>
+    <t>RS-TC-034</t>
+  </si>
+  <si>
+    <t>RS-TC-006
+RS-TC-009
+RS-TC-011
+RS-TC-014
+RS-TC-019
+RS-TC-024
+RS-TC-025
+RS-TC-027
+RS-TC-031</t>
+  </si>
+  <si>
+    <t>Invalid, Existing Email</t>
+  </si>
+  <si>
+    <t>Joshua</t>
+  </si>
+  <si>
+    <t>Cruz</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -606,9 +633,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -646,7 +673,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -752,7 +779,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -894,7 +921,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -903,14 +930,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C45F4C-7522-4BA7-A3CA-2C78A83FEAFA}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="21.1796875" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -921,7 +948,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -932,7 +959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -943,7 +970,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -954,7 +981,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -972,19 +999,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="4" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" customWidth="1"/>
+    <col min="3" max="4" width="11.453125" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
-    <col min="7" max="8" width="16.7109375" customWidth="1"/>
-    <col min="12" max="12" width="19.5703125" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" customWidth="1"/>
+    <col min="7" max="8" width="16.7265625" customWidth="1"/>
+    <col min="12" max="12" width="19.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1022,30 +1049,30 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="137.25">
+    <row r="2" spans="1:12" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" t="s">
-        <v>27</v>
-      </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I2">
         <v>19</v>
@@ -1057,33 +1084,33 @@
         <v>2002</v>
       </c>
       <c r="L2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>30</v>
-      </c>
       <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" t="s">
         <v>26</v>
       </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I3">
         <v>19</v>
@@ -1095,33 +1122,33 @@
         <v>2002</v>
       </c>
       <c r="L3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
         <v>24</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" t="s">
         <v>26</v>
       </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I4">
         <v>19</v>
@@ -1133,33 +1160,33 @@
         <v>2002</v>
       </c>
       <c r="L4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
       <c r="E5" s="8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
         <v>26</v>
       </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I5">
         <v>19</v>
@@ -1171,33 +1198,33 @@
         <v>2002</v>
       </c>
       <c r="L5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>38</v>
       </c>
       <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
       <c r="F6" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I6">
         <v>19</v>
@@ -1209,33 +1236,33 @@
         <v>2002</v>
       </c>
       <c r="L6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>41</v>
       </c>
       <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>23</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>24</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
       </c>
       <c r="F7" s="9">
         <v>12345678900</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I7">
         <v>19</v>
@@ -1247,33 +1274,33 @@
         <v>2002</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>43</v>
       </c>
       <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>24</v>
       </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="9">
-        <v>91234567</v>
+      <c r="F8" s="9" t="s">
+        <v>130</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I8">
         <v>19</v>
@@ -1285,33 +1312,33 @@
         <v>2002</v>
       </c>
       <c r="L8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>24</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="G9" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I9">
         <v>19</v>
@@ -1323,33 +1350,33 @@
         <v>2002</v>
       </c>
       <c r="L9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>23</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>24</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="G10" s="8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I10">
         <v>19</v>
@@ -1361,33 +1388,33 @@
         <v>2002</v>
       </c>
       <c r="L10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>23</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>24</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H11" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I11">
         <v>19</v>
@@ -1399,30 +1426,30 @@
         <v>2002</v>
       </c>
       <c r="L11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
         <v>22</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>23</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>24</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" t="s">
         <v>26</v>
-      </c>
-      <c r="G12" t="s">
-        <v>27</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>16</v>
@@ -1437,46 +1464,126 @@
         <v>2002</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>54</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>134</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="G13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="7">
+        <v>31</v>
+      </c>
+      <c r="J13" s="7">
+        <v>12</v>
+      </c>
+      <c r="K13" s="7">
+        <v>2026</v>
+      </c>
+      <c r="L13" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14">
+        <v>19</v>
+      </c>
+      <c r="J14">
+        <v>9</v>
+      </c>
+      <c r="K14">
+        <v>2002</v>
+      </c>
+      <c r="L14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15">
+        <v>19</v>
+      </c>
+      <c r="J15">
+        <v>9</v>
+      </c>
+      <c r="K15">
+        <v>2002</v>
+      </c>
+      <c r="L15" t="s">
         <v>27</v>
       </c>
-      <c r="H13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13">
-        <v>19</v>
-      </c>
-      <c r="J13">
-        <v>9</v>
-      </c>
-      <c r="K13">
-        <v>2002</v>
-      </c>
-      <c r="L13" t="s">
-        <v>28</v>
-      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" s="6"/>
+      <c r="F16" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1498,18 +1605,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F68DF73-E7CD-4240-9557-2AA4119DA34C}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="1" max="1" width="11.7265625" customWidth="1"/>
+    <col min="2" max="2" width="21.7265625" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" customWidth="1"/>
+    <col min="4" max="4" width="21.54296875" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
-    <col min="7" max="8" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" customWidth="1"/>
+    <col min="7" max="8" width="16.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1523,39 +1630,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="30.75">
+    <row r="2" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="30.75">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="F5" s="5"/>
     </row>
   </sheetData>
@@ -1566,15 +1673,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4C55B6-D732-476E-AEB9-DF4442E1A12D}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" customWidth="1"/>
+    <col min="4" max="4" width="22.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1588,74 +1695,74 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>67</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B4" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
+      <c r="B5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="30.75">
-      <c r="A6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1666,15 +1773,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9EA7360-13D0-453E-8437-7172C5B81D7D}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
     <col min="3" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1685,84 +1792,84 @@
         <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
     </row>
   </sheetData>
@@ -1773,33 +1880,33 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA628117-8171-40AF-9E76-62A43F156754}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" style="6" customWidth="1"/>
     <col min="3" max="3" width="10" style="6" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="23.140625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="34.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="32.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="6"/>
+    <col min="4" max="4" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="23.1796875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="15.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.26953125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.26953125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.1796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>11</v>
@@ -1808,54 +1915,54 @@
         <v>12</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="M1" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="91.5">
+    <row r="2" spans="1:13" ht="87" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="I2" s="6">
         <v>1212</v>
@@ -1864,39 +1971,39 @@
         <v>123</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L2" s="6">
         <v>1000</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="30.75">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F3" s="6">
         <v>12345678912</v>
       </c>
       <c r="G3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I3" s="6">
         <v>1212</v>
@@ -1905,39 +2012,39 @@
         <v>123</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L3" s="6">
         <v>1000</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="30.75">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>107</v>
-      </c>
       <c r="G4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I4" s="6">
         <v>1212</v>
@@ -1946,39 +2053,39 @@
         <v>123</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L4" s="6">
         <v>1000</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I5" s="6">
         <v>1212</v>
@@ -1987,39 +2094,39 @@
         <v>123</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L5" s="6">
         <v>1000</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I6" s="6">
         <v>1212</v>
@@ -2028,36 +2135,36 @@
         <v>123</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L6" s="6">
         <v>10</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="F7" s="14"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="F8" s="14"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="F9" s="12"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="F10" s="12"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="F11" s="12"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="F12" s="12"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="F13" s="15"/>
     </row>
   </sheetData>
@@ -2068,25 +2175,25 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{237319F2-5C9C-4AF4-8EFE-3242F7D6CB15}">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" style="6" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="6" customWidth="1"/>
-    <col min="7" max="10" width="9.140625" style="6"/>
-    <col min="11" max="11" width="11.7109375" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="6"/>
+    <col min="2" max="2" width="30.453125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="22.81640625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.1796875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" style="6" customWidth="1"/>
+    <col min="7" max="10" width="9.1796875" style="6"/>
+    <col min="11" max="11" width="11.7265625" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="9.1796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>2</v>
@@ -2101,118 +2208,118 @@
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="30.75">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B9" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="13" t="s">
+      <c r="E9" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B10" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="B11" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="76.5">
-      <c r="A8" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="30.75">
-      <c r="A9" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="30.75">
-      <c r="A11" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>132</v>
-      </c>
       <c r="E11" s="6" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{677DC8E8-422F-4DEE-A6B2-81373C481FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ccajoles\IdeaProjects\PizzaHutWebsiteTest\src\test\resources\testdata\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92560699-D2A5-4AEE-A20F-B1A82A0B86F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Geolocation_Tracking_Data" sheetId="6" r:id="rId1"/>
@@ -40,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="134">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -286,9 +291,6 @@
     <t>LS-TC-013</t>
   </si>
   <si>
-    <t xml:space="preserve">Password@1234 </t>
-  </si>
-  <si>
     <t>Pre:Requisite: LS-TC-009
 Valid Updated Password</t>
   </si>
@@ -468,7 +470,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -606,9 +608,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -646,7 +648,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -752,7 +754,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -894,7 +896,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -903,14 +905,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C45F4C-7522-4BA7-A3CA-2C78A83FEAFA}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="21.1796875" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -921,7 +923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -932,7 +934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -943,7 +945,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -954,7 +956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -973,18 +975,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="4" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" customWidth="1"/>
+    <col min="3" max="4" width="11.453125" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
-    <col min="7" max="8" width="16.7109375" customWidth="1"/>
-    <col min="12" max="12" width="19.5703125" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" customWidth="1"/>
+    <col min="7" max="8" width="16.7265625" customWidth="1"/>
+    <col min="12" max="12" width="19.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1022,7 +1024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="137.25">
+    <row r="2" spans="1:12" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>21</v>
       </c>
@@ -1060,7 +1062,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1098,7 +1100,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1136,7 +1138,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -1174,7 +1176,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1212,7 +1214,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -1250,7 +1252,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -1288,7 +1290,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -1326,7 +1328,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -1364,7 +1366,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -1402,7 +1404,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>52</v>
       </c>
@@ -1440,7 +1442,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -1498,18 +1500,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F68DF73-E7CD-4240-9557-2AA4119DA34C}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="1" max="1" width="11.7265625" customWidth="1"/>
+    <col min="2" max="2" width="21.7265625" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" customWidth="1"/>
+    <col min="4" max="4" width="21.54296875" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
-    <col min="7" max="8" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" customWidth="1"/>
+    <col min="7" max="8" width="16.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1523,7 +1525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="30.75">
+    <row r="2" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>59</v>
       </c>
@@ -1537,7 +1539,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="30.75">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>63</v>
       </c>
@@ -1552,10 +1554,10 @@
       </c>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="F5" s="5"/>
     </row>
   </sheetData>
@@ -1566,15 +1568,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4C55B6-D732-476E-AEB9-DF4442E1A12D}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" customWidth="1"/>
+    <col min="4" max="4" width="22.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1588,7 +1590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1602,7 +1604,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -1616,7 +1618,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -1630,7 +1632,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -1644,7 +1646,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30.75">
+    <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -1652,10 +1654,10 @@
         <v>67</v>
       </c>
       <c r="C6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1666,15 +1668,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9EA7360-13D0-453E-8437-7172C5B81D7D}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
     <col min="3" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1685,15 +1687,15 @@
         <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>67</v>
@@ -1705,12 +1707,12 @@
         <v>61</v>
       </c>
       <c r="E2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>83</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>75</v>
@@ -1725,26 +1727,26 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>86</v>
       </c>
       <c r="E4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>67</v>
@@ -1753,16 +1755,16 @@
         <v>61</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
     </row>
   </sheetData>
@@ -1773,33 +1775,33 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA628117-8171-40AF-9E76-62A43F156754}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" style="6" customWidth="1"/>
     <col min="3" max="3" width="10" style="6" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="23.140625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="34.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="32.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="6"/>
+    <col min="4" max="4" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="23.1796875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="15.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.26953125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.26953125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.1796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>88</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>89</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>11</v>
@@ -1808,54 +1810,54 @@
         <v>12</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H1" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>95</v>
       </c>
       <c r="M1" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="91.5">
+    <row r="2" spans="1:13" ht="87" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="I2" s="6">
         <v>1212</v>
@@ -1864,7 +1866,7 @@
         <v>123</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L2" s="6">
         <v>1000</v>
@@ -1873,30 +1875,30 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="30.75">
+    <row r="3" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="D3" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="F3" s="6">
         <v>12345678912</v>
       </c>
       <c r="G3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="I3" s="6">
         <v>1212</v>
@@ -1905,7 +1907,7 @@
         <v>123</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L3" s="6">
         <v>1000</v>
@@ -1914,30 +1916,30 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="30.75">
+    <row r="4" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>107</v>
-      </c>
       <c r="G4" t="s">
+        <v>101</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="I4" s="6">
         <v>1212</v>
@@ -1946,39 +1948,39 @@
         <v>123</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L4" s="6">
         <v>1000</v>
       </c>
       <c r="M4" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="6" t="s">
+      <c r="B5" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>110</v>
-      </c>
       <c r="H5" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I5" s="6">
         <v>1212</v>
@@ -1987,7 +1989,7 @@
         <v>123</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L5" s="6">
         <v>1000</v>
@@ -1996,30 +1998,30 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="G6" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="I6" s="6">
         <v>1212</v>
@@ -2028,36 +2030,36 @@
         <v>123</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L6" s="6">
         <v>10</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="F7" s="14"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="F8" s="14"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="F9" s="12"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="F10" s="12"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="F11" s="12"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="F12" s="12"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="F13" s="15"/>
     </row>
   </sheetData>
@@ -2068,25 +2070,25 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{237319F2-5C9C-4AF4-8EFE-3242F7D6CB15}">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" style="6" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="6" customWidth="1"/>
-    <col min="7" max="10" width="9.140625" style="6"/>
-    <col min="11" max="11" width="11.7109375" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="6"/>
+    <col min="2" max="2" width="30.453125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="22.81640625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.1796875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" style="6" customWidth="1"/>
+    <col min="7" max="10" width="9.1796875" style="6"/>
+    <col min="11" max="11" width="11.7265625" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="9.1796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>2</v>
@@ -2101,118 +2103,118 @@
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="6" t="s">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="30.75">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>122</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="6" t="s">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="13" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="13" t="s">
+      <c r="B7" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="E7" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="76.5">
-      <c r="A8" s="17" t="s">
+      <c r="B8" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="E8" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="30.75">
-      <c r="A9" s="17" t="s">
+      <c r="B9" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="E9" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="6" t="s">
+      <c r="B10" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B11" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="30.75">
-      <c r="A11" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>132</v>
-      </c>
       <c r="E11" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ccajoles\IdeaProjects\PizzaHutWebsiteTest\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92560699-D2A5-4AEE-A20F-B1A82A0B86F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48811682-6863-43EC-9830-2611AF7B22F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Geolocation_Tracking_Data" sheetId="6" r:id="rId1"/>
@@ -298,9 +298,6 @@
     <t>Confirm Password</t>
   </si>
   <si>
-    <t>LS-TC-012</t>
-  </si>
-  <si>
     <t>Valid Password Update</t>
   </si>
   <si>
@@ -464,6 +461,9 @@
   </si>
   <si>
     <t>OS-TC-020</t>
+  </si>
+  <si>
+    <t>LS-TC-014</t>
   </si>
 </sst>
 </file>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>67</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>67</v>
@@ -1707,12 +1707,12 @@
         <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>75</v>
@@ -1729,16 +1729,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>46</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>67</v>
@@ -1755,7 +1755,7 @@
         <v>61</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>53</v>
@@ -1798,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>11</v>
@@ -1810,25 +1810,25 @@
         <v>12</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H1" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="10" t="s">
         <v>93</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>94</v>
       </c>
       <c r="M1" s="10" t="s">
         <v>2</v>
@@ -1836,28 +1836,28 @@
     </row>
     <row r="2" spans="1:13" ht="87" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="I2" s="6">
         <v>1212</v>
@@ -1866,7 +1866,7 @@
         <v>123</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L2" s="6">
         <v>1000</v>
@@ -1877,28 +1877,28 @@
     </row>
     <row r="3" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="D3" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="F3" s="6">
         <v>12345678912</v>
       </c>
       <c r="G3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="I3" s="6">
         <v>1212</v>
@@ -1907,7 +1907,7 @@
         <v>123</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L3" s="6">
         <v>1000</v>
@@ -1918,28 +1918,28 @@
     </row>
     <row r="4" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>106</v>
-      </c>
       <c r="G4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="I4" s="6">
         <v>1212</v>
@@ -1948,39 +1948,39 @@
         <v>123</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L4" s="6">
         <v>1000</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>109</v>
-      </c>
       <c r="H5" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I5" s="6">
         <v>1212</v>
@@ -1989,7 +1989,7 @@
         <v>123</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L5" s="6">
         <v>1000</v>
@@ -2000,28 +2000,28 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="G6" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="I6" s="6">
         <v>1212</v>
@@ -2030,13 +2030,13 @@
         <v>123</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L6" s="6">
         <v>10</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -2088,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>2</v>
@@ -2105,24 +2105,24 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
@@ -2130,13 +2130,13 @@
         <v>0</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="10" t="s">
         <v>120</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>121</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>2</v>
@@ -2144,77 +2144,77 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>126</v>
-      </c>
       <c r="E7" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>128</v>
-      </c>
       <c r="E8" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>131</v>
-      </c>
       <c r="E9" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>131</v>
-      </c>
       <c r="E11" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echan\IdeaProjects\selenium_prac\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B01678-61FD-4096-9D12-6A72D6EF44B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A2800C-BD31-42B6-8F30-CB57CD71F0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Geolocation_Tracking_Data" sheetId="6" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="141">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -262,17 +262,11 @@
     <t>LS-TC-013</t>
   </si>
   <si>
-    <t xml:space="preserve">Password@1234 </t>
-  </si>
-  <si>
     <t>Pre:Requisite: LS-TC-009
 Valid Updated Password</t>
   </si>
   <si>
     <t>Confirm Password</t>
-  </si>
-  <si>
-    <t>LS-TC-012</t>
   </si>
   <si>
     <t>Valid Password Update</t>
@@ -464,31 +458,40 @@
     <t>Invalid Birthday (Future date)</t>
   </si>
   <si>
-    <t>RS-TC-011
+    <t>RS-TC-034</t>
+  </si>
+  <si>
+    <t>Invalid, Existing Email</t>
+  </si>
+  <si>
+    <t>Joshua</t>
+  </si>
+  <si>
+    <t>Cruz</t>
+  </si>
+  <si>
+    <t>RS-TC-011 
 RS-TC-035</t>
   </si>
   <si>
-    <t>RS-TC-034</t>
-  </si>
-  <si>
-    <t>RS-TC-006
+    <t>LS-TC-014</t>
+  </si>
+  <si>
+    <t>RS-TC-004
+RS-TC-006
+RS-TC-007
 RS-TC-009
 RS-TC-011
+RS-TC-012
 RS-TC-014
+RS-TC-015
 RS-TC-019
+RS-TC-020
 RS-TC-024
 RS-TC-025
 RS-TC-027
-RS-TC-031</t>
-  </si>
-  <si>
-    <t>Invalid, Existing Email</t>
-  </si>
-  <si>
-    <t>Joshua</t>
-  </si>
-  <si>
-    <t>Cruz</t>
+RS-TC-031
+RS-TC-033</t>
   </si>
 </sst>
 </file>
@@ -1049,9 +1052,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1089,7 +1092,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>28</v>
@@ -1127,7 +1130,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -1294,7 +1297,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G8" t="s">
         <v>26</v>
@@ -1320,16 +1323,16 @@
         <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>25</v>
@@ -1355,19 +1358,19 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
         <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>25</v>
@@ -1393,7 +1396,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
@@ -1431,7 +1434,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
@@ -1469,7 +1472,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s">
         <v>48</v>
@@ -1502,18 +1505,18 @@
         <v>2026</v>
       </c>
       <c r="L13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>134</v>
+      </c>
+      <c r="B14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" t="s">
         <v>137</v>
-      </c>
-      <c r="B14" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14" t="s">
-        <v>141</v>
       </c>
       <c r="D14" t="s">
         <v>49</v>
@@ -1540,12 +1543,12 @@
         <v>2002</v>
       </c>
       <c r="L14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B15" t="s">
         <v>48</v>
@@ -1587,16 +1590,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{CCE1B043-06CC-4013-9A76-E0E181BD7292}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{25906D00-026C-4E5B-A4C4-043FC917215A}"/>
-    <hyperlink ref="E4" r:id="rId3" xr:uid="{4D3EFBC2-78D8-43F5-9BFE-3F3DF10E822D}"/>
-    <hyperlink ref="E6" r:id="rId4" xr:uid="{C1FBCC98-E01D-4D79-8CF2-01A4C5E17F4E}"/>
-    <hyperlink ref="E7" r:id="rId5" xr:uid="{84243ED9-8659-43D8-89F3-60D073EF74DF}"/>
-    <hyperlink ref="E8" r:id="rId6" xr:uid="{304D0317-8016-4EC5-954B-881569CE5577}"/>
-    <hyperlink ref="E9" r:id="rId7" xr:uid="{21831FE6-9910-4DA2-8DCA-1D191425D61D}"/>
-    <hyperlink ref="E10" r:id="rId8" xr:uid="{19C94D56-C143-4371-B0C9-553BCAF9563A}"/>
-    <hyperlink ref="E11" r:id="rId9" xr:uid="{6EA55E52-C67F-498D-B89D-28F9B131C14C}"/>
-    <hyperlink ref="E12" r:id="rId10" xr:uid="{6CA94468-1FE5-4246-AF55-B1C81FAE2103}"/>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{25906D00-026C-4E5B-A4C4-043FC917215A}"/>
+    <hyperlink ref="E4" r:id="rId2" xr:uid="{4D3EFBC2-78D8-43F5-9BFE-3F3DF10E822D}"/>
+    <hyperlink ref="E6" r:id="rId3" xr:uid="{C1FBCC98-E01D-4D79-8CF2-01A4C5E17F4E}"/>
+    <hyperlink ref="E7" r:id="rId4" xr:uid="{84243ED9-8659-43D8-89F3-60D073EF74DF}"/>
+    <hyperlink ref="E8" r:id="rId5" xr:uid="{304D0317-8016-4EC5-954B-881569CE5577}"/>
+    <hyperlink ref="E11" r:id="rId6" xr:uid="{6EA55E52-C67F-498D-B89D-28F9B131C14C}"/>
+    <hyperlink ref="E12" r:id="rId7" xr:uid="{6CA94468-1FE5-4246-AF55-B1C81FAE2103}"/>
+    <hyperlink ref="E2" r:id="rId8" xr:uid="{CCE1B043-06CC-4013-9A76-E0E181BD7292}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1753,16 +1754,16 @@
     </row>
     <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1792,7 +1793,7 @@
         <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -1800,7 +1801,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>60</v>
@@ -1812,12 +1813,12 @@
         <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>68</v>
@@ -1834,16 +1835,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
         <v>40</v>
@@ -1851,7 +1852,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>60</v>
@@ -1860,7 +1861,7 @@
         <v>54</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
         <v>47</v>
@@ -1903,10 +1904,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>11</v>
@@ -1915,25 +1916,25 @@
         <v>12</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H1" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="K1" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="L1" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="M1" s="10" t="s">
         <v>2</v>
@@ -1941,28 +1942,28 @@
     </row>
     <row r="2" spans="1:13" ht="87" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="E2" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="F2" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="H2" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I2" s="6">
         <v>1212</v>
@@ -1971,7 +1972,7 @@
         <v>123</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L2" s="6">
         <v>1000</v>
@@ -1982,28 +1983,28 @@
     </row>
     <row r="3" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="E3" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="F3" s="6">
         <v>12345678912</v>
       </c>
       <c r="G3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I3" s="6">
         <v>1212</v>
@@ -2012,7 +2013,7 @@
         <v>123</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L3" s="6">
         <v>1000</v>
@@ -2023,28 +2024,28 @@
     </row>
     <row r="4" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="E4" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" t="s">
         <v>93</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="G4" t="s">
-        <v>95</v>
-      </c>
       <c r="H4" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I4" s="6">
         <v>1212</v>
@@ -2053,39 +2054,39 @@
         <v>123</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L4" s="6">
         <v>1000</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="E5" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="F5" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F5" s="12" t="s">
+      <c r="G5" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="H5" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I5" s="6">
         <v>1212</v>
@@ -2094,7 +2095,7 @@
         <v>123</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L5" s="6">
         <v>1000</v>
@@ -2105,28 +2106,28 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="E6" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="F6" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="H6" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I6" s="6">
         <v>1212</v>
@@ -2135,13 +2136,13 @@
         <v>123</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L6" s="6">
         <v>10</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -2193,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>2</v>
@@ -2210,24 +2211,24 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
@@ -2235,13 +2236,13 @@
         <v>0</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>115</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>2</v>
@@ -2249,77 +2250,77 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B8" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>122</v>
-      </c>
       <c r="E8" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="E9" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echan\IdeaProjects\selenium_prac\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A2800C-BD31-42B6-8F30-CB57CD71F0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F0420B-F07C-4371-9FFF-AF61F85D433E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Geolocation_Tracking_Data" sheetId="6" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="161">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -379,9 +379,6 @@
     <t>Invalid Voucher</t>
   </si>
   <si>
-    <t>OS-TC-024</t>
-  </si>
-  <si>
     <t>TestingValidVoucher1</t>
   </si>
   <si>
@@ -391,9 +388,6 @@
     <t>Product</t>
   </si>
   <si>
-    <t>Customization</t>
-  </si>
-  <si>
     <t>Variation</t>
   </si>
   <si>
@@ -409,29 +403,7 @@
     <t>OS-TC-016</t>
   </si>
   <si>
-    <t>P1SO PIZZA</t>
-  </si>
-  <si>
-    <t>OS-TC-017</t>
-  </si>
-  <si>
-    <t>Select a Pizza: CHEESE LOVERS
-Select a Pizo Pizza: REGULAR HAWAIIAN PANALO</t>
-  </si>
-  <si>
-    <t>OS-TC-018</t>
-  </si>
-  <si>
-    <t>SEAFOOD SUPREME</t>
-  </si>
-  <si>
-    <t>Regular (9" Good for 2-3)</t>
-  </si>
-  <si>
     <t>OS-TC-019</t>
-  </si>
-  <si>
-    <t>OS-TC-020</t>
   </si>
   <si>
     <t>RS-TC-005</t>
@@ -493,12 +465,99 @@
 RS-TC-031
 RS-TC-033</t>
   </si>
+  <si>
+    <t>OS-TC-001</t>
+  </si>
+  <si>
+    <t>Filter</t>
+  </si>
+  <si>
+    <t>OS-TC-005</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Limited Time Offer</t>
+  </si>
+  <si>
+    <t>For Me!</t>
+  </si>
+  <si>
+    <t>For 2!</t>
+  </si>
+  <si>
+    <t>For 4+</t>
+  </si>
+  <si>
+    <t>OS-TC-007</t>
+  </si>
+  <si>
+    <t>Expected Result (Voucher)</t>
+  </si>
+  <si>
+    <t>Expected Result (Cart)</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Best Sellers</t>
+  </si>
+  <si>
+    <t>Meat-Free</t>
+  </si>
+  <si>
+    <t>Spicy</t>
+  </si>
+  <si>
+    <t>OS-TC-010</t>
+  </si>
+  <si>
+    <t>MEAT LOVERS</t>
+  </si>
+  <si>
+    <t>OS-TC-014</t>
+  </si>
+  <si>
+    <t>OS-TC-022</t>
+  </si>
+  <si>
+    <t>Customization1</t>
+  </si>
+  <si>
+    <t>Customization2</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>Pan Pizza</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>Regular (9" Good for 2-3) Pan Pizza</t>
+  </si>
+  <si>
+    <t>OS-TC-041</t>
+  </si>
+  <si>
+    <t>Large (12" Good for 4-6) Mega Crunch Pizza</t>
+  </si>
+  <si>
+    <t>OS-TC-017</t>
+  </si>
+  <si>
+    <t>FATHER'S DAY DUO PIZZA REGULAR</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -541,9 +600,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -572,7 +638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -610,8 +676,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -932,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C45F4C-7522-4BA7-A3CA-2C78A83FEAFA}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.81640625" customWidth="1"/>
@@ -992,6 +1061,17 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1054,7 +1134,7 @@
     </row>
     <row r="2" spans="1:12" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1092,7 +1172,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>28</v>
@@ -1130,7 +1210,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -1297,7 +1377,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="G8" t="s">
         <v>26</v>
@@ -1358,7 +1438,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s">
         <v>48</v>
@@ -1396,7 +1476,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
@@ -1434,7 +1514,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
@@ -1472,7 +1552,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="B13" t="s">
         <v>48</v>
@@ -1505,18 +1585,18 @@
         <v>2026</v>
       </c>
       <c r="L13" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D14" t="s">
         <v>49</v>
@@ -1543,12 +1623,12 @@
         <v>2002</v>
       </c>
       <c r="L14" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B15" t="s">
         <v>48</v>
@@ -1754,7 +1834,7 @@
     </row>
     <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>60</v>
@@ -2175,21 +2255,24 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{237319F2-5C9C-4AF4-8EFE-3242F7D6CB15}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" style="6" customWidth="1"/>
     <col min="2" max="2" width="30.453125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="22.81640625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="14.1796875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="11.453125" style="6" customWidth="1"/>
-    <col min="7" max="10" width="9.1796875" style="6"/>
-    <col min="11" max="11" width="11.7265625" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="9.1796875" style="6"/>
+    <col min="3" max="3" width="28.1796875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="26.08984375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="17" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.54296875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="23.26953125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="24.26953125" style="6" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" style="6" customWidth="1"/>
+    <col min="10" max="11" width="9.1796875" style="6"/>
+    <col min="12" max="12" width="11.7265625" style="6" customWidth="1"/>
+    <col min="13" max="16384" width="9.1796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -2197,21 +2280,34 @@
         <v>104</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
+        <v>141</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>133</v>
+      </c>
       <c r="J1" s="10"/>
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M1" s="10"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>106</v>
@@ -2220,110 +2316,193 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" s="10" t="s">
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="B5" s="13"/>
+      <c r="D5" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="6" t="s">
+    </row>
+    <row r="6" spans="1:13" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>115</v>
       </c>
+      <c r="B6" s="13"/>
+      <c r="D6" s="6" t="s">
+        <v>148</v>
+      </c>
       <c r="E6" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="D8" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="I10" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>116</v>
+        <v>134</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="I12" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echan\IdeaProjects\selenium_prac\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F0420B-F07C-4371-9FFF-AF61F85D433E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A01B4F8-0D0E-43D6-A966-316DC8D7C91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Geolocation_Tracking_Data" sheetId="6" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="171">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -262,19 +262,12 @@
     <t>LS-TC-013</t>
   </si>
   <si>
-    <t>Pre:Requisite: LS-TC-009
-Valid Updated Password</t>
-  </si>
-  <si>
     <t>Confirm Password</t>
   </si>
   <si>
     <t>Valid Password Update</t>
   </si>
   <si>
-    <t>LS-TC-009</t>
-  </si>
-  <si>
     <t>LS-TC-010</t>
   </si>
   <si>
@@ -311,17 +304,6 @@
     <t>Change</t>
   </si>
   <si>
-    <t>CS-TC-005
-CS-TC-006
-CS-TC-007
-CS-TC-011
-CS-TC-013
-CS-TC-022</t>
-  </si>
-  <si>
-    <t>Tomrrow</t>
-  </si>
-  <si>
     <t>01:00 PM</t>
   </si>
   <si>
@@ -359,9 +341,6 @@
   </si>
   <si>
     <t>abc</t>
-  </si>
-  <si>
-    <t>CS-TC-014</t>
   </si>
   <si>
     <t>Invalid Change</t>
@@ -552,12 +531,63 @@
   <si>
     <t>FATHER'S DAY DUO PIZZA REGULAR</t>
   </si>
+  <si>
+    <t>Tomorrow</t>
+  </si>
+  <si>
+    <t>LS-TC-008</t>
+  </si>
+  <si>
+    <t>LS-TC-017</t>
+  </si>
+  <si>
+    <t>Pre:Requisite: LS-TC-009</t>
+  </si>
+  <si>
+    <t>Valid Updated Password</t>
+  </si>
+  <si>
+    <t>Invalid Empty Credentials</t>
+  </si>
+  <si>
+    <t>CS-TC-011</t>
+  </si>
+  <si>
+    <t>CS-TC-016</t>
+  </si>
+  <si>
+    <t>Valid Schedule</t>
+  </si>
+  <si>
+    <t>LS-TC-016</t>
+  </si>
+  <si>
+    <t>LS-TC-015</t>
+  </si>
+  <si>
+    <t>LS-TC-012</t>
+  </si>
+  <si>
+    <t>Invalid Empty Password</t>
+  </si>
+  <si>
+    <t>Invalid Empty Email</t>
+  </si>
+  <si>
+    <t>CS-TC-006
+CS-TC-007
+CS-TC-012
+CS-TC-014
+CS-TC-017
+CS-TC-028
+CS-TC-029</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -590,13 +620,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -611,8 +634,38 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -623,6 +676,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF09797"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF09797"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -638,7 +697,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -658,28 +717,51 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="18" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1066,7 +1148,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -1134,7 +1216,7 @@
     </row>
     <row r="2" spans="1:12" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1172,7 +1254,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>28</v>
@@ -1210,7 +1292,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -1377,7 +1459,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G8" t="s">
         <v>26</v>
@@ -1438,7 +1520,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s">
         <v>48</v>
@@ -1476,7 +1558,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
@@ -1514,7 +1596,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
@@ -1552,7 +1634,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B13" t="s">
         <v>48</v>
@@ -1585,18 +1667,18 @@
         <v>2026</v>
       </c>
       <c r="L13" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B14" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D14" t="s">
         <v>49</v>
@@ -1623,12 +1705,12 @@
         <v>2002</v>
       </c>
       <c r="L14" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B15" t="s">
         <v>48</v>
@@ -1753,7 +1835,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4C55B6-D732-476E-AEB9-DF4442E1A12D}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1763,97 +1845,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="15" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B5" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="C5" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="20" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>71</v>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="16" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9EA7360-13D0-453E-8437-7172C5B81D7D}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.26953125" customWidth="1"/>
@@ -1863,97 +1968,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B5" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C5" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D6" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="22"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="21"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="16" t="s">
+        <v>169</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1980,273 +2131,363 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="G1" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="10" t="s">
+      <c r="I1" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="10" t="s">
+      <c r="J1" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="K1" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="L1" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="M1" s="23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="D2" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="M1" s="10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="87" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="E2" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="F2" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="G2" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="H2" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="I2" s="20">
+        <v>1212</v>
+      </c>
+      <c r="J2" s="20">
+        <v>123</v>
+      </c>
+      <c r="K2" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="L2" s="20">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="25">
+        <v>12345678912</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="I3" s="20">
+        <v>1212</v>
+      </c>
+      <c r="J3" s="20">
+        <v>123</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="L3" s="20">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" s="20">
+        <v>1212</v>
+      </c>
+      <c r="J4" s="20">
+        <v>123</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="L4" s="20">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="I5" s="20">
+        <v>1212</v>
+      </c>
+      <c r="J5" s="20">
+        <v>123</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="L5" s="20">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="I6" s="20">
+        <v>1212</v>
+      </c>
+      <c r="J6" s="20">
+        <v>123</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="L6" s="25">
+        <v>10</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="I2" s="6">
-        <v>1212</v>
-      </c>
-      <c r="J2" s="6">
-        <v>123</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="L2" s="6">
-        <v>1000</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="6">
-        <v>12345678912</v>
-      </c>
-      <c r="G3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="I3" s="6">
-        <v>1212</v>
-      </c>
-      <c r="J3" s="6">
-        <v>123</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="L3" s="6">
-        <v>1000</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="G4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="I4" s="6">
-        <v>1212</v>
-      </c>
-      <c r="J4" s="6">
-        <v>123</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="L4" s="6">
-        <v>1000</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="I5" s="6">
-        <v>1212</v>
-      </c>
-      <c r="J5" s="6">
-        <v>123</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="L5" s="6">
-        <v>1000</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="I6" s="6">
-        <v>1212</v>
-      </c>
-      <c r="J6" s="6">
-        <v>123</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="L6" s="6">
-        <v>10</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="F7" s="14"/>
+      <c r="B7" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="F8" s="14"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="F9" s="12"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="F10" s="12"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="F11" s="12"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="F12" s="12"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="F13" s="15"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2273,32 +2514,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>104</v>
+      <c r="B1" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J1" s="10"/>
       <c r="K1" s="10"/>
@@ -2307,202 +2548,202 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B5" s="13"/>
+        <v>107</v>
+      </c>
+      <c r="B5" s="11"/>
       <c r="D5" s="6" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" s="13"/>
+        <v>110</v>
+      </c>
+      <c r="B6" s="11"/>
       <c r="D6" s="6" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="18" t="s">
-        <v>159</v>
+      <c r="A7" s="14" t="s">
+        <v>154</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="E7" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>154</v>
+      <c r="F7" s="13" t="s">
+        <v>149</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>158</v>
+        <v>143</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>153</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
+        <v>129</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
       <c r="I10" s="6" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B12" s="10"/>
       <c r="I12" s="6" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I13" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>158</v>
+        <v>143</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -22,6 +22,7 @@
     <sheet name="Ordering_Data" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -737,8 +738,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -754,7 +753,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="18" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -764,6 +762,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1915,13 +1916,13 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="29" t="s">
         <v>54</v>
       </c>
       <c r="D6" s="20" t="s">
@@ -1929,9 +1930,9 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="21"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="21"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="29"/>
       <c r="D7" s="20" t="s">
         <v>160</v>
       </c>
@@ -1988,16 +1989,16 @@
       <c r="A2" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="29" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2005,10 +2006,10 @@
       <c r="A3" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
@@ -2048,16 +2049,16 @@
       <c r="A6" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="29" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2065,10 +2066,10 @@
       <c r="A7" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="21"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="29"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
@@ -2131,43 +2132,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="K1" s="24" t="s">
+      <c r="K1" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="L1" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="M1" s="23" t="s">
+      <c r="M1" s="21" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2178,7 +2179,7 @@
       <c r="B2" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="26" t="s">
         <v>85</v>
       </c>
       <c r="D2" s="20" t="s">
@@ -2187,7 +2188,7 @@
       <c r="E2" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="28" t="s">
         <v>88</v>
       </c>
       <c r="G2" s="20" t="s">
@@ -2219,7 +2220,7 @@
       <c r="B3" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="26" t="s">
         <v>85</v>
       </c>
       <c r="D3" s="20" t="s">
@@ -2228,7 +2229,7 @@
       <c r="E3" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="23">
         <v>12345678912</v>
       </c>
       <c r="G3" s="16" t="s">
@@ -2260,7 +2261,7 @@
       <c r="B4" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="26" t="s">
         <v>85</v>
       </c>
       <c r="D4" s="20" t="s">
@@ -2269,7 +2270,7 @@
       <c r="E4" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="27" t="s">
         <v>94</v>
       </c>
       <c r="G4" s="16" t="s">
@@ -2301,7 +2302,7 @@
       <c r="B5" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="26" t="s">
         <v>85</v>
       </c>
       <c r="D5" s="20" t="s">
@@ -2310,10 +2311,10 @@
       <c r="E5" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="23" t="s">
         <v>97</v>
       </c>
       <c r="H5" s="20" t="s">
@@ -2342,7 +2343,7 @@
       <c r="B6" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="26" t="s">
         <v>85</v>
       </c>
       <c r="D6" s="20" t="s">
@@ -2351,7 +2352,7 @@
       <c r="E6" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="28" t="s">
         <v>88</v>
       </c>
       <c r="G6" s="20" t="s">
@@ -2369,7 +2370,7 @@
       <c r="K6" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="L6" s="25">
+      <c r="L6" s="23">
         <v>10</v>
       </c>
       <c r="M6" s="20" t="s">
@@ -2383,7 +2384,7 @@
       <c r="B7" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="26" t="s">
         <v>85</v>
       </c>
       <c r="D7" s="20"/>
@@ -2405,7 +2406,7 @@
       <c r="C8" s="20"/>
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
-      <c r="F8" s="26"/>
+      <c r="F8" s="24"/>
       <c r="G8" s="20"/>
       <c r="H8" s="20"/>
       <c r="I8" s="20"/>
@@ -2436,8 +2437,8 @@
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
       <c r="I10" s="20"/>
       <c r="J10" s="20"/>
       <c r="K10" s="20"/>
@@ -2480,7 +2481,7 @@
       <c r="C13" s="20"/>
       <c r="D13" s="20"/>
       <c r="E13" s="20"/>
-      <c r="F13" s="27"/>
+      <c r="F13" s="25"/>
       <c r="G13" s="20"/>
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echan\IdeaProjects\selenium_prac\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A01B4F8-0D0E-43D6-A966-316DC8D7C91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C495714-2A64-4D5F-A777-51C46C9C600D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Geolocation_Tracking_Data" sheetId="6" r:id="rId1"/>
@@ -22,7 +22,6 @@
     <sheet name="Ordering_Data" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -46,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="170">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -371,19 +370,10 @@
     <t>Variation</t>
   </si>
   <si>
-    <t>OS-TC-015</t>
-  </si>
-  <si>
     <t>PEPSI 1.5L</t>
   </si>
   <si>
     <t>Added to cart</t>
-  </si>
-  <si>
-    <t>OS-TC-016</t>
-  </si>
-  <si>
-    <t>OS-TC-019</t>
   </si>
   <si>
     <t>RS-TC-005</t>
@@ -452,9 +442,6 @@
     <t>Filter</t>
   </si>
   <si>
-    <t>OS-TC-005</t>
-  </si>
-  <si>
     <t>All</t>
   </si>
   <si>
@@ -470,9 +457,6 @@
     <t>For 4+</t>
   </si>
   <si>
-    <t>OS-TC-007</t>
-  </si>
-  <si>
     <t>Expected Result (Voucher)</t>
   </si>
   <si>
@@ -491,15 +475,9 @@
     <t>Spicy</t>
   </si>
   <si>
-    <t>OS-TC-010</t>
-  </si>
-  <si>
     <t>MEAT LOVERS</t>
   </si>
   <si>
-    <t>OS-TC-014</t>
-  </si>
-  <si>
     <t>OS-TC-022</t>
   </si>
   <si>
@@ -519,12 +497,6 @@
   </si>
   <si>
     <t>Regular (9" Good for 2-3) Pan Pizza</t>
-  </si>
-  <si>
-    <t>OS-TC-041</t>
-  </si>
-  <si>
-    <t>Large (12" Good for 4-6) Mega Crunch Pizza</t>
   </si>
   <si>
     <t>OS-TC-017</t>
@@ -582,6 +554,33 @@
 CS-TC-017
 CS-TC-028
 CS-TC-029</t>
+  </si>
+  <si>
+    <t>OS-TC-006</t>
+  </si>
+  <si>
+    <t>OS-TC-008</t>
+  </si>
+  <si>
+    <t>OS-TC-011</t>
+  </si>
+  <si>
+    <t>OS-TC-018</t>
+  </si>
+  <si>
+    <t>CARBONARA SUPREME</t>
+  </si>
+  <si>
+    <t>CS-TC-001  123 Shaw Boulevard  Valid Address</t>
+  </si>
+  <si>
+    <t>OS-TC-040</t>
+  </si>
+  <si>
+    <t>OS-TC-015
+OS-TC-025
+OS-TC-026
+OS-TC-027</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C45F4C-7522-4BA7-A3CA-2C78A83FEAFA}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.81640625" customWidth="1"/>
@@ -1149,13 +1148,18 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -1217,7 +1221,7 @@
     </row>
     <row r="2" spans="1:12" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1255,7 +1259,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>28</v>
@@ -1293,7 +1297,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -1460,7 +1464,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G8" t="s">
         <v>26</v>
@@ -1521,7 +1525,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
         <v>48</v>
@@ -1559,7 +1563,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
@@ -1597,7 +1601,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
@@ -1635,7 +1639,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B13" t="s">
         <v>48</v>
@@ -1668,18 +1672,18 @@
         <v>2026</v>
       </c>
       <c r="L13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" t="s">
         <v>120</v>
-      </c>
-      <c r="B14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14" t="s">
-        <v>123</v>
       </c>
       <c r="D14" t="s">
         <v>49</v>
@@ -1706,12 +1710,12 @@
         <v>2002</v>
       </c>
       <c r="L14" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s">
         <v>48</v>
@@ -1861,7 +1865,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>60</v>
@@ -1917,7 +1921,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="29" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>60</v>
@@ -1926,7 +1930,7 @@
         <v>54</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -1934,7 +1938,7 @@
       <c r="B7" s="30"/>
       <c r="C7" s="29"/>
       <c r="D7" s="20" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -1944,7 +1948,7 @@
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
       <c r="D8" s="16" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -1987,7 +1991,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B2" s="30" t="s">
         <v>60</v>
@@ -2004,7 +2008,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="29"/>
@@ -2047,7 +2051,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>60</v>
@@ -2064,7 +2068,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="20" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="29"/>
@@ -2073,7 +2077,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>60</v>
@@ -2081,7 +2085,7 @@
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
       <c r="E8" s="16" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -2092,7 +2096,7 @@
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
       <c r="E9" s="16" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2174,10 +2178,10 @@
     </row>
     <row r="2" spans="1:13" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C2" s="26" t="s">
         <v>85</v>
@@ -2218,7 +2222,7 @@
         <v>93</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C3" s="26" t="s">
         <v>85</v>
@@ -2259,7 +2263,7 @@
         <v>96</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C4" s="26" t="s">
         <v>85</v>
@@ -2297,10 +2301,10 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C5" s="26" t="s">
         <v>85</v>
@@ -2338,10 +2342,10 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>85</v>
@@ -2382,7 +2386,7 @@
         <v>92</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C7" s="26" t="s">
         <v>85</v>
@@ -2397,7 +2401,7 @@
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
       <c r="M7" s="20" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -2497,7 +2501,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{237319F2-5C9C-4AF4-8EFE-3242F7D6CB15}">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" style="6" customWidth="1"/>
@@ -2522,25 +2526,25 @@
         <v>99</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>105</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>106</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J1" s="10"/>
       <c r="K1" s="10"/>
@@ -2549,7 +2553,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>101</v>
@@ -2569,179 +2573,152 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="B5" s="11"/>
       <c r="D5" s="6" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="B6" s="11"/>
       <c r="D6" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>150</v>
-      </c>
       <c r="G6" s="6" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="11" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="I9" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="I11" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="I10" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B12" s="10"/>
+        <v>162</v>
+      </c>
       <c r="I12" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>153</v>
-      </c>
+      <c r="E18" s="11"/>
+      <c r="G18" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echan\IdeaProjects\selenium_prac\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C495714-2A64-4D5F-A777-51C46C9C600D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEAD128-FDC4-4211-8FFE-99479E75F0B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Geolocation_Tracking_Data" sheetId="6" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="170">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -571,9 +571,6 @@
     <t>CARBONARA SUPREME</t>
   </si>
   <si>
-    <t>CS-TC-001  123 Shaw Boulevard  Valid Address</t>
-  </si>
-  <si>
     <t>OS-TC-040</t>
   </si>
   <si>
@@ -581,6 +578,9 @@
 OS-TC-025
 OS-TC-026
 OS-TC-027</t>
+  </si>
+  <si>
+    <t>CS-TC-001</t>
   </si>
 </sst>
 </file>
@@ -1159,7 +1159,13 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>167</v>
+        <v>169</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2575,7 +2581,7 @@
     </row>
     <row r="4" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>107</v>
@@ -2586,7 +2592,7 @@
     </row>
     <row r="5" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B5" s="11"/>
       <c r="D5" s="6" t="s">

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echan\IdeaProjects\selenium_prac\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEAD128-FDC4-4211-8FFE-99479E75F0B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027C05C8-C172-40EA-8BCB-7A69D10DB28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Geolocation_Tracking_Data" sheetId="6" r:id="rId1"/>
@@ -499,9 +499,6 @@
     <t>Regular (9" Good for 2-3) Pan Pizza</t>
   </si>
   <si>
-    <t>OS-TC-017</t>
-  </si>
-  <si>
     <t>FATHER'S DAY DUO PIZZA REGULAR</t>
   </si>
   <si>
@@ -581,6 +578,10 @@
   </si>
   <si>
     <t>CS-TC-001</t>
+  </si>
+  <si>
+    <t>OS-TC-016
+OS-TC-017</t>
   </si>
 </sst>
 </file>
@@ -1159,7 +1160,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -1871,7 +1872,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>60</v>
@@ -1927,7 +1928,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="29" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>60</v>
@@ -1936,7 +1937,7 @@
         <v>54</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -1944,7 +1945,7 @@
       <c r="B7" s="30"/>
       <c r="C7" s="29"/>
       <c r="D7" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -1954,7 +1955,7 @@
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
       <c r="D8" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1998,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B2" s="30" t="s">
         <v>60</v>
@@ -2014,7 +2015,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="29"/>
@@ -2074,7 +2075,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="29"/>
@@ -2083,7 +2084,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>60</v>
@@ -2091,7 +2092,7 @@
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
       <c r="E8" s="16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -2102,7 +2103,7 @@
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
       <c r="E9" s="16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2184,10 +2185,10 @@
     </row>
     <row r="2" spans="1:13" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C2" s="26" t="s">
         <v>85</v>
@@ -2228,7 +2229,7 @@
         <v>93</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" s="26" t="s">
         <v>85</v>
@@ -2269,7 +2270,7 @@
         <v>96</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C4" s="26" t="s">
         <v>85</v>
@@ -2307,10 +2308,10 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C5" s="26" t="s">
         <v>85</v>
@@ -2348,10 +2349,10 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>85</v>
@@ -2392,7 +2393,7 @@
         <v>92</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C7" s="26" t="s">
         <v>85</v>
@@ -2407,7 +2408,7 @@
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
       <c r="M7" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -2581,7 +2582,7 @@
     </row>
     <row r="4" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>107</v>
@@ -2592,11 +2593,11 @@
     </row>
     <row r="5" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B5" s="11"/>
       <c r="D5" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>108</v>
@@ -2604,7 +2605,7 @@
     </row>
     <row r="6" spans="1:13" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="B6" s="11"/>
       <c r="D6" s="6" t="s">
@@ -2622,12 +2623,12 @@
     </row>
     <row r="7" spans="1:13" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>141</v>
@@ -2641,7 +2642,7 @@
     </row>
     <row r="8" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>126</v>
@@ -2649,7 +2650,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
@@ -2659,7 +2660,7 @@
     </row>
     <row r="10" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>128</v>
@@ -2667,7 +2668,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B11" s="10"/>
       <c r="I11" s="6" t="s">
@@ -2676,7 +2677,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>130</v>
@@ -2684,7 +2685,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>133</v>
@@ -2692,7 +2693,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>134</v>
@@ -2700,7 +2701,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>135</v>
@@ -2708,7 +2709,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>136</v>
@@ -2716,7 +2717,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>133</v>
